--- a/dama/cases/营收系统数据标准/2 服务类/2.3 表具管理数据/2.3.1 表具基础信息/2. IC卡主表.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.3 表具管理数据/2.3.1 表具基础信息/2. IC卡主表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="174">
   <si>
     <t>业务属性</t>
   </si>
@@ -235,7 +235,7 @@
     <t>表具基础信息</t>
   </si>
   <si>
-    <t>水表绑定的表卡唯一档案编号。</t>
+    <t>客户所绑定或持有的水表（IC卡）表卡编号，外键关联表卡信息。</t>
   </si>
   <si>
     <t>主键，表卡唯一标识，非空。</t>
@@ -292,7 +292,7 @@
     <t>CARD_TYPE</t>
   </si>
   <si>
-    <t>水表对应的卡片/终端硬件类型。</t>
+    <t>表卡类型代码，包括IC卡表、智能表。</t>
   </si>
   <si>
     <t>1: IC卡, 2: 智能表，非空。</t>
@@ -307,7 +307,7 @@
     <t>数值</t>
   </si>
   <si>
-    <t>符合字段类型及业务字典约束</t>
+    <t>1-IC卡、2-智能表。</t>
   </si>
   <si>
     <t>RCM_SELF_METERID</t>
@@ -319,7 +319,7 @@
     <t>SELF_METERID</t>
   </si>
   <si>
-    <t>水表在特定区域或内部管理中的自编号码。</t>
+    <t>水表自编号，水表管理用唯一编号。</t>
   </si>
   <si>
     <t>内部资产自编号码。</t>
@@ -328,6 +328,9 @@
     <t>仅允许字符及数字</t>
   </si>
   <si>
+    <t>与水表档案一致。</t>
+  </si>
+  <si>
     <t>否</t>
   </si>
   <si>
@@ -340,12 +343,15 @@
     <t>BUY_TIMES</t>
   </si>
   <si>
-    <t>表卡累计执行的购水/充值次数。</t>
+    <t>累计充值/购水次数。</t>
   </si>
   <si>
     <t>大于等于0的整数，非空。</t>
   </si>
   <si>
+    <t>非负整数。</t>
+  </si>
+  <si>
     <t>RCM_TOTAL_WATER</t>
   </si>
   <si>
@@ -355,7 +361,7 @@
     <t>TOTAL_WATER</t>
   </si>
   <si>
-    <t>表卡历史累计购买的水量总和（吨/m³）。</t>
+    <t>累计购水总量（立方米）。</t>
   </si>
   <si>
     <t>大于等于0的数值，非空。</t>
@@ -364,6 +370,9 @@
     <t>吨</t>
   </si>
   <si>
+    <t>≥0，单位立方米，两位小数。</t>
+  </si>
+  <si>
     <t>RCM_BALANCE</t>
   </si>
   <si>
@@ -373,7 +382,7 @@
     <t>BALANCE</t>
   </si>
   <si>
-    <t>表卡当前账户中剩余的可用资金余额。</t>
+    <t>表卡账户余额（元）。</t>
   </si>
   <si>
     <t>精准至4位小数的金额数值，非空。</t>
@@ -382,6 +391,9 @@
     <t>元</t>
   </si>
   <si>
+    <t>可为负（欠费），单位元，四位小数。</t>
+  </si>
+  <si>
     <t>RCM_STATE</t>
   </si>
   <si>
@@ -391,7 +403,7 @@
     <t>STATE</t>
   </si>
   <si>
-    <t>表卡当前的业务运行与生命周期状态。</t>
+    <t>表卡状态代码，包括正常、作废。</t>
   </si>
   <si>
     <t>0:正常, -1:作废，非空。</t>
@@ -400,7 +412,7 @@
     <t>TYPE_CARD_STATE</t>
   </si>
   <si>
-    <t>0-正常，-1-作废</t>
+    <t>0-正常、-1-作废。</t>
   </si>
   <si>
     <t>RCM_CREATOR_ID</t>
@@ -412,12 +424,15 @@
     <t>CREATOR_ID</t>
   </si>
   <si>
-    <t>建档生成该表卡记录的系统操作员工号。</t>
+    <t>创建时由登录用户写入。</t>
   </si>
   <si>
     <t>系统操作员工号ID，非空。</t>
   </si>
   <si>
+    <t>有效操作员工号。</t>
+  </si>
+  <si>
     <t>RCM_CREATE_TIME</t>
   </si>
   <si>
@@ -427,7 +442,7 @@
     <t>CREATE_TIME</t>
   </si>
   <si>
-    <t>该表卡建档发卡的时间戳。</t>
+    <t>记录创建时间。</t>
   </si>
   <si>
     <t>标准日期时间格式，非空。</t>
@@ -442,6 +457,9 @@
     <t>YYYY-MM-DD HH:24:MI:SS</t>
   </si>
   <si>
+    <t>合法日期时间。</t>
+  </si>
+  <si>
     <t>RCM_MODIFIER_ID</t>
   </si>
   <si>
@@ -451,7 +469,7 @@
     <t>MODIFIER_ID</t>
   </si>
   <si>
-    <t>最后更新表卡状态或充值信息的系统操作员ID。</t>
+    <t>修改时由登录用户写入。</t>
   </si>
   <si>
     <t>RCM_MODIFY_TIME</t>
@@ -463,43 +481,7 @@
     <t>MODIFY_TIME</t>
   </si>
   <si>
-    <t>表卡数据最后一次变更维护的时间戳。</t>
-  </si>
-  <si>
-    <t>RCM_METER_CARD_TYPE</t>
-  </si>
-  <si>
-    <t>表卡类型</t>
-  </si>
-  <si>
-    <t>METER_CARD_TYPE</t>
-  </si>
-  <si>
-    <t>细分的表卡规格与芯片分类识别码。</t>
-  </si>
-  <si>
-    <t>关联表卡规格字典。</t>
-  </si>
-  <si>
-    <t>TYPE_METER_CARD_TYPE</t>
-  </si>
-  <si>
-    <t>RCM_BUY_AREA</t>
-  </si>
-  <si>
-    <t>写卡区域</t>
-  </si>
-  <si>
-    <t>BUY_AREA</t>
-  </si>
-  <si>
-    <t>IC卡读写操作所归属的区域代码。</t>
-  </si>
-  <si>
-    <t>关联写卡区域字典。</t>
-  </si>
-  <si>
-    <t>TYPE_BUY_AREA</t>
+    <t>记录最后修改时间。</t>
   </si>
   <si>
     <t>RCM_IS_OPEN</t>
@@ -511,7 +493,7 @@
     <t>IS_OPEN</t>
   </si>
   <si>
-    <t>标识表卡是否已经完成初始化并开卡启用。</t>
+    <t>是否开卡标志，包括未开卡和已开卡。</t>
   </si>
   <si>
     <t>1:已开卡, 0:未开卡。</t>
@@ -520,7 +502,7 @@
     <t>TYPE_FLAG_YN</t>
   </si>
   <si>
-    <t>0-否，1-是</t>
+    <t>0-未开卡、1-已开卡。</t>
   </si>
   <si>
     <t>RCM_SUBCOM_CODE</t>
@@ -532,10 +514,10 @@
     <t>SUBCOM_CODE</t>
   </si>
   <si>
-    <t>开卡或服务归属的供水营业所/站点机构代码。</t>
-  </si>
-  <si>
-    <t>营业站点机构编码。</t>
+    <t>客户所属营业站点编码，外键关联营业站点表。</t>
+  </si>
+  <si>
+    <t>须匹配营业站点编码。</t>
   </si>
   <si>
     <t>RCM_TOTAL_MONEY</t>
@@ -547,10 +529,13 @@
     <t>TOTAL_MONEY</t>
   </si>
   <si>
-    <t>表卡历史累计购买水费的总金额。</t>
+    <t>累计购买金额（元）。</t>
   </si>
   <si>
     <t>精准至4位小数的金额数值。</t>
+  </si>
+  <si>
+    <t>≥0，单位元，四位小数。</t>
   </si>
 </sst>
 </file>
@@ -596,11 +581,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -977,7 +960,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -997,6 +980,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1101,19 +1099,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1122,7 +1120,7 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1131,13 +1129,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1155,28 +1153,28 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1185,10 +1183,10 @@
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1246,7 +1244,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1261,6 +1259,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1660,7 +1661,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -1705,35 +1706,35 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="7" t="s">
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="12" t="s">
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="16" t="s">
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="17" t="s">
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="17"/>
+      <c r="AD1" s="18"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:30">
       <c r="A2" s="2" t="s">
@@ -1769,61 +1770,61 @@
       <c r="K2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="S2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="T2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="W2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="13" t="s">
+      <c r="X2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="Y2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="18" t="s">
+      <c r="Z2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="AA2" s="18" t="s">
+      <c r="AA2" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="AB2" s="18" t="s">
+      <c r="AB2" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AC2" s="19" t="s">
+      <c r="AC2" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" s="19" t="s">
+      <c r="AD2" s="20" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1861,61 +1862,61 @@
       <c r="K3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="T3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="U3" s="14" t="s">
+      <c r="U3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="V3" s="14" t="s">
+      <c r="V3" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="W3" s="14" t="s">
+      <c r="W3" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="X3" s="14" t="s">
+      <c r="X3" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" s="14" t="s">
+      <c r="Y3" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="Z3" s="20" t="s">
+      <c r="Z3" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="AA3" s="20" t="s">
+      <c r="AA3" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="AB3" s="20" t="s">
+      <c r="AB3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="AC3" s="21" t="s">
+      <c r="AC3" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="AD3" s="21" t="s">
+      <c r="AD3" s="22" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1941,7 +1942,7 @@
       <c r="G4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>73</v>
       </c>
       <c r="I4" s="5" t="s">
@@ -1971,10 +1972,10 @@
       <c r="Q4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="15">
+      <c r="R4" s="16">
         <v>20</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="16" t="s">
         <v>75</v>
       </c>
       <c r="T4" s="4" t="s">
@@ -1998,7 +1999,7 @@
       <c r="Z4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA4" s="22" t="s">
+      <c r="AA4" s="23" t="s">
         <v>85</v>
       </c>
       <c r="AB4" s="4" t="s">
@@ -2033,7 +2034,7 @@
       <c r="G5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>92</v>
       </c>
       <c r="I5" s="5" t="s">
@@ -2063,10 +2064,10 @@
       <c r="Q5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="R5" s="15">
+      <c r="R5" s="16">
         <v>22</v>
       </c>
-      <c r="S5" s="15">
+      <c r="S5" s="16">
         <v>0</v>
       </c>
       <c r="T5" s="4" t="s">
@@ -2090,7 +2091,7 @@
       <c r="Z5" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA5" s="4" t="s">
+      <c r="AA5" s="6" t="s">
         <v>97</v>
       </c>
       <c r="AB5" s="4" t="s">
@@ -2125,7 +2126,7 @@
       <c r="G6" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>101</v>
       </c>
       <c r="I6" s="5" t="s">
@@ -2155,10 +2156,10 @@
       <c r="Q6" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="R6" s="15">
+      <c r="R6" s="16">
         <v>30</v>
       </c>
-      <c r="S6" s="15" t="s">
+      <c r="S6" s="16" t="s">
         <v>75</v>
       </c>
       <c r="T6" s="4" t="s">
@@ -2182,11 +2183,11 @@
       <c r="Z6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AA6" s="4" t="s">
-        <v>97</v>
+      <c r="AA6" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC6" s="4" t="s">
         <v>87</v>
@@ -2197,13 +2198,13 @@
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:30">
       <c r="A7" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>69</v>
@@ -2217,11 +2218,11 @@
       <c r="G7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>108</v>
+      <c r="H7" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>75</v>
@@ -2247,10 +2248,10 @@
       <c r="Q7" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="R7" s="15">
+      <c r="R7" s="16">
         <v>22</v>
       </c>
-      <c r="S7" s="15">
+      <c r="S7" s="16">
         <v>0</v>
       </c>
       <c r="T7" s="4" t="s">
@@ -2274,8 +2275,8 @@
       <c r="Z7" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA7" s="4" t="s">
-        <v>97</v>
+      <c r="AA7" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="AB7" s="4" t="s">
         <v>86</v>
@@ -2289,13 +2290,13 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:30">
       <c r="A8" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>69</v>
@@ -2309,11 +2310,11 @@
       <c r="G8" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>113</v>
+      <c r="H8" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>75</v>
@@ -2339,14 +2340,14 @@
       <c r="Q8" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="R8" s="15">
+      <c r="R8" s="16">
         <v>22</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="16">
         <v>0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="U8" s="4" t="s">
         <v>80</v>
@@ -2366,8 +2367,8 @@
       <c r="Z8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA8" s="4" t="s">
-        <v>97</v>
+      <c r="AA8" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="AB8" s="4" t="s">
         <v>86</v>
@@ -2381,13 +2382,13 @@
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:30">
       <c r="A9" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>69</v>
@@ -2401,11 +2402,11 @@
       <c r="G9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>119</v>
+      <c r="H9" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>75</v>
@@ -2431,14 +2432,14 @@
       <c r="Q9" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="R9" s="15">
+      <c r="R9" s="16">
         <v>22</v>
       </c>
-      <c r="S9" s="15">
+      <c r="S9" s="16">
         <v>4</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="U9" s="4" t="s">
         <v>80</v>
@@ -2458,8 +2459,8 @@
       <c r="Z9" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA9" s="4" t="s">
-        <v>97</v>
+      <c r="AA9" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="AB9" s="4" t="s">
         <v>86</v>
@@ -2473,13 +2474,13 @@
     </row>
     <row r="10" ht="26" customHeight="1" spans="1:30">
       <c r="A10" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>69</v>
@@ -2493,17 +2494,17 @@
       <c r="G10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>125</v>
+      <c r="H10" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>75</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>76</v>
@@ -2523,10 +2524,10 @@
       <c r="Q10" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="R10" s="15">
+      <c r="R10" s="16">
         <v>22</v>
       </c>
-      <c r="S10" s="15">
+      <c r="S10" s="16">
         <v>0</v>
       </c>
       <c r="T10" s="4" t="s">
@@ -2550,8 +2551,8 @@
       <c r="Z10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA10" s="4" t="s">
-        <v>128</v>
+      <c r="AA10" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="AB10" s="4" t="s">
         <v>86</v>
@@ -2565,13 +2566,13 @@
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:30">
       <c r="A11" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>69</v>
@@ -2585,11 +2586,11 @@
       <c r="G11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>132</v>
+      <c r="H11" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>75</v>
@@ -2615,10 +2616,10 @@
       <c r="Q11" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="16">
         <v>22</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="16">
         <v>0</v>
       </c>
       <c r="T11" s="4" t="s">
@@ -2642,8 +2643,8 @@
       <c r="Z11" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA11" s="4" t="s">
-        <v>97</v>
+      <c r="AA11" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="AB11" s="4" t="s">
         <v>86</v>
@@ -2657,13 +2658,13 @@
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:30">
       <c r="A12" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>69</v>
@@ -2677,11 +2678,11 @@
       <c r="G12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>137</v>
+      <c r="H12" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>75</v>
@@ -2702,15 +2703,15 @@
         <v>77</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="R12" s="15">
+        <v>145</v>
+      </c>
+      <c r="R12" s="16">
         <v>7</v>
       </c>
-      <c r="S12" s="15" t="s">
+      <c r="S12" s="16" t="s">
         <v>75</v>
       </c>
       <c r="T12" s="4" t="s">
@@ -2732,10 +2733,10 @@
         <v>83</v>
       </c>
       <c r="Z12" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA12" s="4" t="s">
-        <v>97</v>
+        <v>146</v>
+      </c>
+      <c r="AA12" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="AB12" s="4" t="s">
         <v>86</v>
@@ -2749,13 +2750,13 @@
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:30">
       <c r="A13" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>69</v>
@@ -2769,11 +2770,11 @@
       <c r="G13" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>145</v>
+      <c r="H13" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>75</v>
@@ -2799,10 +2800,10 @@
       <c r="Q13" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="R13" s="15">
+      <c r="R13" s="16">
         <v>22</v>
       </c>
-      <c r="S13" s="15">
+      <c r="S13" s="16">
         <v>0</v>
       </c>
       <c r="T13" s="4" t="s">
@@ -2826,8 +2827,8 @@
       <c r="Z13" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA13" s="4" t="s">
-        <v>97</v>
+      <c r="AA13" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="AB13" s="4" t="s">
         <v>86</v>
@@ -2841,13 +2842,13 @@
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:30">
       <c r="A14" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>69</v>
@@ -2861,11 +2862,11 @@
       <c r="G14" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>149</v>
+      <c r="H14" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>75</v>
@@ -2886,15 +2887,15 @@
         <v>77</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="R14" s="15">
+        <v>145</v>
+      </c>
+      <c r="R14" s="16">
         <v>7</v>
       </c>
-      <c r="S14" s="15" t="s">
+      <c r="S14" s="16" t="s">
         <v>75</v>
       </c>
       <c r="T14" s="4" t="s">
@@ -2916,10 +2917,10 @@
         <v>83</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA14" s="4" t="s">
-        <v>97</v>
+        <v>146</v>
+      </c>
+      <c r="AA14" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="AB14" s="4" t="s">
         <v>86</v>
@@ -2933,13 +2934,13 @@
     </row>
     <row r="15" ht="26" customHeight="1" spans="1:30">
       <c r="A15" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>69</v>
@@ -2953,17 +2954,17 @@
       <c r="G15" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>153</v>
+      <c r="H15" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>75</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>76</v>
@@ -2983,10 +2984,10 @@
       <c r="Q15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="R15" s="15">
+      <c r="R15" s="16">
         <v>22</v>
       </c>
-      <c r="S15" s="15">
+      <c r="S15" s="16">
         <v>0</v>
       </c>
       <c r="T15" s="4" t="s">
@@ -3010,11 +3011,11 @@
       <c r="Z15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA15" s="4" t="s">
-        <v>97</v>
+      <c r="AA15" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC15" s="4" t="s">
         <v>87</v>
@@ -3025,13 +3026,13 @@
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:30">
       <c r="A16" s="4" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>69</v>
@@ -3045,17 +3046,17 @@
       <c r="G16" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>160</v>
+      <c r="H16" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>75</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>76</v>
@@ -3070,16 +3071,16 @@
         <v>77</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="R16" s="15">
-        <v>22</v>
-      </c>
-      <c r="S16" s="15">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="R16" s="16">
+        <v>10</v>
+      </c>
+      <c r="S16" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="T16" s="4" t="s">
         <v>75</v>
@@ -3100,13 +3101,13 @@
         <v>83</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA16" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
+      </c>
+      <c r="AA16" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="AB16" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC16" s="4" t="s">
         <v>87</v>
@@ -3117,13 +3118,13 @@
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:30">
       <c r="A17" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>69</v>
@@ -3137,17 +3138,17 @@
       <c r="G17" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>165</v>
+      <c r="H17" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>75</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>167</v>
+        <v>75</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>76</v>
@@ -3167,14 +3168,14 @@
       <c r="Q17" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="R17" s="15">
+      <c r="R17" s="16">
         <v>22</v>
       </c>
-      <c r="S17" s="15">
-        <v>0</v>
+      <c r="S17" s="16">
+        <v>4</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="U17" s="4" t="s">
         <v>80</v>
@@ -3194,200 +3195,16 @@
       <c r="Z17" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA17" s="4" t="s">
-        <v>168</v>
+      <c r="AA17" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="AB17" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AC17" s="4" t="s">
         <v>87</v>
       </c>
       <c r="AD17" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1" spans="1:30">
-      <c r="A18" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="R18" s="15">
-        <v>10</v>
-      </c>
-      <c r="S18" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="T18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="U18" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="V18" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="W18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="X18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y18" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z18" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB18" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC18" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD18" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1" spans="1:30">
-      <c r="A19" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q19" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="R19" s="15">
-        <v>22</v>
-      </c>
-      <c r="S19" s="15">
-        <v>4</v>
-      </c>
-      <c r="T19" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="U19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="W19" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="X19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y19" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z19" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA19" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB19" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC19" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD19" s="4" t="s">
         <v>88</v>
       </c>
     </row>
